--- a/data/french_works.xlsx
+++ b/data/french_works.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F314"/>
+  <dimension ref="A1:G314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -438,6 +427,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,6 +461,11 @@
           <t>matiere</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>matiere_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -497,6 +492,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -523,6 +523,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -549,6 +554,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -575,6 +585,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -601,6 +616,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -627,6 +647,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -653,6 +678,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -679,6 +709,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -705,6 +740,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -731,6 +771,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -757,6 +802,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -783,6 +833,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -809,6 +864,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -835,6 +895,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -861,6 +926,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -887,6 +957,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -913,6 +988,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -939,6 +1019,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -965,6 +1050,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -991,6 +1081,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1017,6 +1112,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1043,6 +1143,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1069,6 +1174,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1095,6 +1205,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1121,6 +1236,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1147,6 +1267,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1173,6 +1298,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1199,6 +1329,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1225,6 +1360,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1251,6 +1391,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1277,6 +1422,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1303,6 +1453,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1329,6 +1484,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1355,6 +1515,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1381,6 +1546,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1407,6 +1577,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1433,6 +1608,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1459,6 +1639,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1485,6 +1670,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1511,6 +1701,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1537,6 +1732,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1563,6 +1763,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1589,6 +1794,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1615,6 +1825,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1641,6 +1856,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1667,6 +1887,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1693,6 +1918,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1719,6 +1949,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1745,6 +1980,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1771,6 +2011,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1797,6 +2042,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1823,6 +2073,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1849,6 +2104,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1875,6 +2135,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1901,6 +2166,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1927,6 +2197,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1953,6 +2228,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1979,6 +2259,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2005,6 +2290,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2031,6 +2321,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2057,6 +2352,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2083,6 +2383,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2109,6 +2414,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2135,6 +2445,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2161,6 +2476,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2187,6 +2507,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2213,6 +2538,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2239,6 +2569,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2265,6 +2600,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2291,6 +2631,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2317,6 +2662,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2343,6 +2693,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2369,6 +2724,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2395,6 +2755,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2421,6 +2786,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2447,6 +2817,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2473,6 +2848,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2499,6 +2879,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2525,6 +2910,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2551,6 +2941,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2577,6 +2972,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2603,6 +3003,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2629,6 +3034,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2655,6 +3065,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2681,6 +3096,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2707,6 +3127,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2733,6 +3158,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2759,6 +3189,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2785,6 +3220,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2811,6 +3251,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2837,6 +3282,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2863,6 +3313,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2889,6 +3344,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2915,6 +3375,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2941,6 +3406,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2967,6 +3437,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2993,6 +3468,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3019,6 +3499,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3045,6 +3530,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3071,6 +3561,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3097,6 +3592,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3123,6 +3623,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3149,6 +3654,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3175,6 +3685,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3201,6 +3716,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3227,6 +3747,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3253,6 +3778,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3279,6 +3809,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3305,6 +3840,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3331,6 +3871,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3357,6 +3902,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3383,6 +3933,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3409,6 +3964,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -3435,6 +3995,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -3461,6 +4026,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3487,6 +4057,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3513,6 +4088,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -3539,6 +4119,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -3565,6 +4150,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -3591,6 +4181,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -3617,6 +4212,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3643,6 +4243,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3669,6 +4274,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3695,6 +4305,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3721,6 +4336,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3747,6 +4367,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3773,6 +4398,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3799,6 +4429,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3825,6 +4460,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3851,6 +4491,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3877,6 +4522,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3903,6 +4553,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3929,6 +4584,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3955,6 +4615,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3981,6 +4646,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -4007,6 +4677,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -4033,6 +4708,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -4059,6 +4739,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -4085,6 +4770,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -4111,6 +4801,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -4137,6 +4832,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -4163,6 +4863,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -4189,6 +4894,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -4215,6 +4925,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4241,6 +4956,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -4267,6 +4987,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -4293,6 +5018,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -4319,6 +5049,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -4345,6 +5080,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -4371,6 +5111,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -4397,6 +5142,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -4423,6 +5173,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -4449,6 +5204,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -4475,6 +5235,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -4501,6 +5266,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -4527,6 +5297,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -4553,6 +5328,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -4579,6 +5359,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -4605,6 +5390,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -4631,6 +5421,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -4657,6 +5452,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -4683,6 +5483,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -4709,6 +5514,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -4735,6 +5545,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -4761,6 +5576,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -4787,6 +5607,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -4813,6 +5638,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -4839,6 +5669,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -4865,6 +5700,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -4891,6 +5731,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -4917,6 +5762,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -4943,6 +5793,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -4969,6 +5824,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -4995,6 +5855,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -5021,6 +5886,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -5047,6 +5917,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -5073,6 +5948,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -5099,6 +5979,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -5125,6 +6010,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -5151,6 +6041,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -5177,6 +6072,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -5203,6 +6103,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -5229,6 +6134,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -5255,6 +6165,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -5281,6 +6196,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -5307,6 +6227,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -5333,6 +6258,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -5359,6 +6289,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -5385,6 +6320,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -5411,6 +6351,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -5437,6 +6382,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -5463,6 +6413,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -5489,6 +6444,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -5515,6 +6475,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -5541,6 +6506,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -5567,6 +6537,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -5593,6 +6568,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -5619,6 +6599,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -5645,6 +6630,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -5671,6 +6661,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -5697,6 +6692,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -5723,6 +6723,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -5749,6 +6754,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -5775,6 +6785,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -5801,6 +6816,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -5827,6 +6847,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -5853,6 +6878,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -5879,6 +6909,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -5905,6 +6940,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -5931,6 +6971,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -5957,6 +7002,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -5983,6 +7033,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -6009,6 +7064,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -6035,6 +7095,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -6061,6 +7126,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -6087,6 +7157,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -6113,6 +7188,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -6139,6 +7219,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -6165,6 +7250,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -6191,6 +7281,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -6217,6 +7312,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -6243,6 +7343,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -6269,6 +7374,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -6295,6 +7405,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -6321,6 +7436,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -6347,6 +7467,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -6373,6 +7498,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -6399,6 +7529,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -6425,6 +7560,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -6451,6 +7591,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -6477,6 +7622,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -6503,6 +7653,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -6529,6 +7684,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -6555,6 +7715,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -6581,6 +7746,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -6607,6 +7777,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -6633,6 +7808,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -6659,6 +7839,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -6685,6 +7870,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -6711,6 +7901,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -6737,6 +7932,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -6763,6 +7963,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -6789,6 +7994,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -6815,6 +8025,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -6841,6 +8056,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -6867,6 +8087,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -6893,6 +8118,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -6919,6 +8149,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -6945,6 +8180,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -6971,6 +8211,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -6997,6 +8242,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -7023,6 +8273,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -7049,6 +8304,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -7075,6 +8335,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -7101,6 +8366,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -7127,6 +8397,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -7153,6 +8428,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -7179,6 +8459,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -7205,6 +8490,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -7231,6 +8521,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -7257,6 +8552,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -7283,6 +8583,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -7309,6 +8614,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -7335,6 +8645,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -7361,6 +8676,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -7387,6 +8707,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -7413,6 +8738,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -7439,6 +8769,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -7465,6 +8800,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -7491,6 +8831,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -7517,6 +8862,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -7543,6 +8893,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -7569,6 +8924,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -7595,6 +8955,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -7621,6 +8986,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -7647,6 +9017,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -7673,6 +9048,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -7699,6 +9079,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -7725,6 +9110,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -7751,6 +9141,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -7777,6 +9172,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -7803,6 +9203,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -7829,6 +9234,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -7855,6 +9265,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -7881,6 +9296,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -7907,6 +9327,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -7933,6 +9358,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -7959,6 +9389,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -7985,6 +9420,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -8011,6 +9451,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -8037,6 +9482,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -8063,6 +9513,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -8089,6 +9544,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -8115,6 +9575,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -8141,6 +9606,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -8167,6 +9637,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -8193,6 +9668,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -8219,6 +9699,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -8245,6 +9730,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -8271,6 +9761,11 @@
           <t>France</t>
         </is>
       </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -8297,6 +9792,11 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -8323,6 +9823,11 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -8349,6 +9854,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -8375,6 +9885,11 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -8401,6 +9916,11 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -8427,6 +9947,11 @@
           <t>Britain</t>
         </is>
       </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -8453,6 +9978,11 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -8479,6 +10009,11 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -8505,6 +10040,11 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -8531,6 +10071,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -8557,6 +10102,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -8583,6 +10133,11 @@
           <t>Rome</t>
         </is>
       </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -8607,6 +10162,11 @@
       <c r="F314" t="inlineStr">
         <is>
           <t>Rome</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>override</t>
         </is>
       </c>
     </row>

--- a/data/french_works.xlsx
+++ b/data/french_works.xlsx
@@ -7448,7 +7448,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Renaut de Montauban, 1re version, 'Vulgate'</t>
+          <t>Renaut de Montauban, 1re version, 'Vulgate</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">

--- a/data/french_works.xlsx
+++ b/data/french_works.xlsx
@@ -9789,12 +9789,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -9820,12 +9820,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -9882,12 +9882,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -9913,12 +9913,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -9975,12 +9975,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -10006,12 +10006,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -10037,12 +10037,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>override</t>
         </is>
       </c>
     </row>

--- a/data/french_works.xlsx
+++ b/data/french_works.xlsx
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>

--- a/data/french_works.xlsx
+++ b/data/french_works.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,13 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5728,12 +5739,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
     </row>

--- a/data/french_works.xlsx
+++ b/data/french_works.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +427,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/data/french_works.xlsx
+++ b/data/french_works.xlsx
@@ -469,11 +469,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>586</v>
+        <v>48750</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aliscans</t>
+          <t>Eracle</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,14 +482,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="E2" t="n">
-        <v>1200</v>
+        <v>1186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -500,42 +500,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>48859</v>
+        <v>48744</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Comte d'Anjou</t>
+          <t>Erec et Enide</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1314</v>
+        <v>1441</v>
       </c>
       <c r="E3" t="n">
-        <v>1316</v>
+        <v>1465</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50237</v>
+        <v>652</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Guiron le courtois, Continuation</t>
+          <t>Garin le Lorrain</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -544,14 +544,14 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1241</v>
+        <v>1181</v>
       </c>
       <c r="E4" t="n">
-        <v>1280</v>
+        <v>1200</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -562,11 +562,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>48992</v>
+        <v>654</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joseph d'Arimathie</t>
+          <t>Girbert de Metz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -575,14 +575,14 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1201</v>
+        <v>1181</v>
       </c>
       <c r="E5" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -593,11 +593,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>49106</v>
+        <v>50233</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lancelot</t>
+          <t>Guiron le courtois</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1211</v>
+        <v>1236</v>
       </c>
       <c r="E6" t="n">
         <v>1240</v>
@@ -624,11 +624,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>50230</v>
+        <v>48958</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meliadus</t>
+          <t>Hunbaut</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -640,7 +640,7 @@
         <v>1226</v>
       </c>
       <c r="E7" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,11 +655,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>49027</v>
+        <v>671</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Merlin</t>
+          <t>Jehan de Lanson</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -671,11 +671,11 @@
         <v>1201</v>
       </c>
       <c r="E8" t="n">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -686,11 +686,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>48960</v>
+        <v>49006</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Merveilles de Rigomer</t>
+          <t>Joseph d'Arimathie Vulgate ou Estoire del Saint Graal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1241</v>
+        <v>1215</v>
       </c>
       <c r="E9" t="n">
-        <v>1260</v>
+        <v>1235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -717,11 +717,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>49134</v>
+        <v>48992</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mort Artu</t>
+          <t>Joseph d'Arimathie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -733,7 +733,7 @@
         <v>1201</v>
       </c>
       <c r="E10" t="n">
-        <v>1235</v>
+        <v>1300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -748,11 +748,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>50316</v>
+        <v>50194</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Naissance du chevalier au cygne Elioxe-Beatrix (version hybride)</t>
+          <t>Joufroi de Poitiers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -761,14 +761,14 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1181</v>
+        <v>1241</v>
       </c>
       <c r="E11" t="n">
-        <v>1220</v>
+        <v>1260</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -779,11 +779,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>731</v>
+        <v>49106</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Otinel</t>
+          <t>Lancelot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -792,14 +792,14 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1151</v>
+        <v>1211</v>
       </c>
       <c r="E12" t="n">
-        <v>1250</v>
+        <v>1240</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -810,11 +810,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>48572</v>
+        <v>49102</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Perceval</t>
+          <t>Lancelot</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1196</v>
+        <v>1173</v>
       </c>
       <c r="E13" t="n">
-        <v>1210</v>
+        <v>1182</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -841,11 +841,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>48573</v>
+        <v>49513</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Perlesvaus</t>
+          <t>Marques de Rome</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -854,14 +854,14 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1201</v>
+        <v>1251</v>
       </c>
       <c r="E14" t="n">
-        <v>1240</v>
+        <v>1277</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -872,11 +872,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>49127</v>
+        <v>48947</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>queste del Saint Graal</t>
+          <t>Meliacin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -885,14 +885,14 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1215</v>
+        <v>1276</v>
       </c>
       <c r="E15" t="n">
-        <v>1235</v>
+        <v>1294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -903,11 +903,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>50238</v>
+        <v>50230</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Suite Guiron</t>
+          <t>Meliadus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1241</v>
+        <v>1226</v>
       </c>
       <c r="E16" t="n">
-        <v>1270</v>
+        <v>1250</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -934,73 +934,73 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>49139</v>
+        <v>48808</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tristan</t>
+          <t>Mélusine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1226</v>
+        <v>1392</v>
       </c>
       <c r="E17" t="n">
-        <v>1235</v>
+        <v>1393</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>48765</v>
+        <v>48811</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yvain ou le chevalier au lion</t>
+          <t>Melusine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1173</v>
+        <v>1396</v>
       </c>
       <c r="E18" t="n">
-        <v>1186</v>
+        <v>1410</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>49785</v>
+        <v>49027</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abladane</t>
+          <t>Merlin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,14 +1009,14 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1256</v>
+        <v>1201</v>
       </c>
       <c r="E19" t="n">
-        <v>1293</v>
+        <v>1225</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1027,11 +1027,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>584</v>
+        <v>744</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aie d'Avignon</t>
+          <t>Moniage Guillaume, 2e rédaction (longue)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="E20" t="n">
-        <v>1205</v>
+        <v>1190</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1058,11 +1058,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>764</v>
+        <v>49134</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aimeri de Narbonne</t>
+          <t>Mort Artu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1071,14 +1071,14 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1181</v>
+        <v>1201</v>
       </c>
       <c r="E21" t="n">
-        <v>1225</v>
+        <v>1235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1089,11 +1089,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>623</v>
+        <v>677</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aiol</t>
+          <t>Naissance du chevalier au cygne Beatrix</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1201</v>
+        <v>1181</v>
       </c>
       <c r="E22" t="n">
         <v>1220</v>
@@ -1120,11 +1120,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>48501</v>
+        <v>48477</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alexandre en Orient</t>
+          <t>Parthonopeus de Blois</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1133,29 +1133,29 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1165</v>
+        <v>1176</v>
       </c>
       <c r="E23" t="n">
-        <v>1200</v>
+        <v>1188</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>48506</v>
+        <v>48573</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Perlesvaus</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1164,14 +1164,14 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1176</v>
+        <v>1201</v>
       </c>
       <c r="E24" t="n">
-        <v>1190</v>
+        <v>1240</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1182,11 +1182,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>48500</v>
+        <v>749</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Prise d' Orange</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1195,14 +1195,14 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="E25" t="n">
-        <v>1165</v>
+        <v>1220</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1213,11 +1213,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>588</v>
+        <v>750</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ami et Amile</t>
+          <t>Prise de Cordres et de Sebille</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="E26" t="n">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1244,11 +1244,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>48581</v>
+        <v>49141</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ami et Amile</t>
+          <t>Propheties de Merlin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1257,14 +1257,14 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1301</v>
+        <v>1267</v>
       </c>
       <c r="E27" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1275,27 +1275,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>589</v>
+        <v>48565</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ami et Amile</t>
+          <t>Quatrième continuation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1381</v>
+        <v>1226</v>
       </c>
       <c r="E28" t="n">
-        <v>1500</v>
+        <v>1230</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1306,11 +1306,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>713</v>
+        <v>49127</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anseïs de Carthage</t>
+          <t>queste del Saint Graal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1319,14 +1319,14 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1200</v>
+        <v>1215</v>
       </c>
       <c r="E29" t="n">
-        <v>1250</v>
+        <v>1235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1337,11 +1337,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>592</v>
+        <v>668</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Anseïs de Metz</t>
+          <t>Renaut de Montauban</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1121</v>
+        <v>1181</v>
       </c>
       <c r="E30" t="n">
-        <v>1250</v>
+        <v>1200</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1368,23 +1368,23 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>47611</v>
+        <v>48783</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Anséis de Metz</t>
+          <t>Roland</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1467</v>
+        <v>1196</v>
       </c>
       <c r="E31" t="n">
-        <v>1500</v>
+        <v>1205</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1399,42 +1399,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>775</v>
+        <v>48787</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Antioche</t>
+          <t>Roland</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1181</v>
+        <v>1401</v>
       </c>
       <c r="E32" t="n">
-        <v>1200</v>
+        <v>1433</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>48733</v>
+        <v>752</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Artus de Bretagne</t>
+          <t>Saisnes</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1443,14 +1443,14 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1276</v>
+        <v>1181</v>
       </c>
       <c r="E33" t="n">
-        <v>1320</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1461,11 +1461,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>596</v>
+        <v>49292</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aspremont</t>
+          <t>Sept Sages de Rome, version A</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1474,14 +1474,14 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1184</v>
+        <v>1201</v>
       </c>
       <c r="E34" t="n">
-        <v>1192</v>
+        <v>1278</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1492,11 +1492,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>597</v>
+        <v>49290</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Auberi le Bourgoing</t>
+          <t>Sept Sages de Rome, version C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1505,29 +1505,29 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1100</v>
+        <v>1167</v>
       </c>
       <c r="E35" t="n">
         <v>1250</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>598</v>
+        <v>49419</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Auberon</t>
+          <t>Sept Sages de Rome, Version L</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1536,14 +1536,14 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1261</v>
+        <v>1201</v>
       </c>
       <c r="E36" t="n">
-        <v>1311</v>
+        <v>1233</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1554,11 +1554,11 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>513</v>
+        <v>692</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Audigier</t>
+          <t>Simon de Pouille</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1181</v>
+        <v>1201</v>
       </c>
       <c r="E37" t="n">
-        <v>1220</v>
+        <v>1250</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1579,17 +1579,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>709</v>
+        <v>48773</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bataille Loquifer</t>
+          <t>Sone de Nansay</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1598,29 +1598,29 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1166</v>
+        <v>1251</v>
       </c>
       <c r="E38" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>720</v>
+        <v>49088</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bâtard de Bouillon</t>
+          <t>Suite Vulgate du Merlin</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1629,29 +1629,29 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1301</v>
+        <v>1231</v>
       </c>
       <c r="E39" t="n">
-        <v>1355</v>
+        <v>1235</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>599</v>
+        <v>48381</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Baudouin de Sebourc</t>
+          <t>Tristan et Iseut</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1660,138 +1660,138 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1314</v>
+        <v>1146</v>
       </c>
       <c r="E40" t="n">
-        <v>1350</v>
+        <v>1200</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>716</v>
+        <v>49139</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Belle Hélène de Constantinople</t>
+          <t>Tristan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1341</v>
+        <v>1226</v>
       </c>
       <c r="E41" t="n">
-        <v>1360</v>
+        <v>1235</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>47643</v>
+        <v>48516</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Belle Hélène de Constantinople</t>
+          <t>Troie</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1401</v>
+        <v>1161</v>
       </c>
       <c r="E42" t="n">
-        <v>1500</v>
+        <v>1170</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>47644</v>
+        <v>48518</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Belle Hélène de Constantinople</t>
+          <t>Troie, prose 1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1448</v>
+        <v>1274</v>
       </c>
       <c r="E43" t="n">
-        <v>1448</v>
+        <v>1287</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>48822</v>
+        <v>48562</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Berinus</t>
+          <t>Troisième continuation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1346</v>
+        <v>1201</v>
       </c>
       <c r="E44" t="n">
-        <v>1375</v>
+        <v>1237</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1802,11 +1802,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>602</v>
+        <v>48979</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Berte au grand pied</t>
+          <t>Yder</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1815,14 +1815,14 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1273</v>
+        <v>1201</v>
       </c>
       <c r="E45" t="n">
-        <v>1285</v>
+        <v>1233</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1833,23 +1833,23 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>603</v>
+        <v>707</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bertrand Du Guesclin</t>
+          <t>Agolant</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1376</v>
+        <v>1180</v>
       </c>
       <c r="E46" t="n">
-        <v>1390</v>
+        <v>1220</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>48464</v>
+        <v>584</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blancandin</t>
+          <t>Aie d'Avignon</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1877,91 +1877,91 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1201</v>
+        <v>1167</v>
       </c>
       <c r="E47" t="n">
-        <v>1233</v>
+        <v>1205</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>48467</v>
+        <v>764</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Blancandin</t>
+          <t>Aimeri de Narbonne</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1463</v>
+        <v>1181</v>
       </c>
       <c r="E48" t="n">
-        <v>1472</v>
+        <v>1225</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48466</v>
+        <v>48506</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Blancandin</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1460</v>
+        <v>1176</v>
       </c>
       <c r="E49" t="n">
-        <v>1469</v>
+        <v>1190</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>48568</v>
+        <v>586</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bliocadran</t>
+          <t>Aliscans</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1970,14 +1970,14 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1201</v>
+        <v>1151</v>
       </c>
       <c r="E50" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -1988,23 +1988,23 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>604</v>
+        <v>713</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Brun de la Montagne</t>
+          <t>Anseïs de Carthage</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1351</v>
+        <v>1200</v>
       </c>
       <c r="E51" t="n">
-        <v>1400</v>
+        <v>1250</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2013,17 +2013,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>717</v>
+        <v>592</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bueve d'Aigremont</t>
+          <t>Anseïs de Metz</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1201</v>
+        <v>1121</v>
       </c>
       <c r="E52" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2050,11 +2050,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>689</v>
+        <v>775</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bueve de Commarchis</t>
+          <t>Antioche</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2063,29 +2063,29 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1272</v>
+        <v>1181</v>
       </c>
       <c r="E53" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>605</v>
+        <v>715</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bueve de Hanstonne cont. 1</t>
+          <t>Aquin</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2094,14 +2094,14 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1200</v>
+        <v>1101</v>
       </c>
       <c r="E54" t="n">
-        <v>1225</v>
+        <v>1300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2112,11 +2112,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>607</v>
+        <v>48733</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bueve de Hanstonne cont. 3</t>
+          <t>Artus de Bretagne</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2125,14 +2125,14 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1221</v>
+        <v>1276</v>
       </c>
       <c r="E55" t="n">
-        <v>1300</v>
+        <v>1320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2143,27 +2143,27 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>48462</v>
+        <v>596</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bueve de Hanstonne</t>
+          <t>Aspremont</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1460</v>
+        <v>1184</v>
       </c>
       <c r="E56" t="n">
-        <v>1469</v>
+        <v>1192</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2174,27 +2174,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>48735</v>
+        <v>597</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cardenois et Passebeauté</t>
+          <t>Auberi le Bourgoing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1376</v>
+        <v>1100</v>
       </c>
       <c r="E57" t="n">
-        <v>1400</v>
+        <v>1250</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2205,42 +2205,42 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>49515</v>
+        <v>716</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cassidorus</t>
+          <t>Belle Hélène de Constantinople</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1271</v>
+        <v>1341</v>
       </c>
       <c r="E58" t="n">
-        <v>1280</v>
+        <v>1360</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>47608</v>
+        <v>47643</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Charlemagne et Anseïs</t>
+          <t>Belle Hélène de Constantinople</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>718</v>
+        <v>48817</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Charlemagne</t>
+          <t>Berinus</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2280,14 +2280,14 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1296</v>
+        <v>1241</v>
       </c>
       <c r="E60" t="n">
-        <v>1314</v>
+        <v>1260</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2298,11 +2298,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>719</v>
+        <v>48822</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Charles le Chauve</t>
+          <t>Berinus</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2311,29 +2311,29 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1355</v>
+        <v>1346</v>
       </c>
       <c r="E61" t="n">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Charroi de Nimes</t>
+          <t>Berte au grand pied</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1101</v>
+        <v>1273</v>
       </c>
       <c r="E62" t="n">
-        <v>1160</v>
+        <v>1285</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2360,27 +2360,27 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>48471</v>
+        <v>603</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chastelain de Coucy</t>
+          <t>Bertrand Du Guesclin</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1281</v>
+        <v>1376</v>
       </c>
       <c r="E63" t="n">
-        <v>1300</v>
+        <v>1390</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2391,23 +2391,23 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>48473</v>
+        <v>48464</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chastelain de Coucy</t>
+          <t>Blancandin</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1459</v>
+        <v>1201</v>
       </c>
       <c r="E64" t="n">
-        <v>1468</v>
+        <v>1233</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2422,11 +2422,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>524</v>
+        <v>717</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chetifs</t>
+          <t>Bueve d'Aigremont</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2435,29 +2435,29 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1181</v>
+        <v>1201</v>
       </c>
       <c r="E65" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>721</v>
+        <v>607</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chevalerie Ogier de Danemarche</t>
+          <t>Bueve de Hanstonne cont. 3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2466,14 +2466,14 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1151</v>
+        <v>1221</v>
       </c>
       <c r="E66" t="n">
-        <v>1225</v>
+        <v>1300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2484,11 +2484,11 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>615</v>
+        <v>49515</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chevalerie Ogier en alexandrins</t>
+          <t>Cassidorus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2497,14 +2497,14 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1328</v>
+        <v>1271</v>
       </c>
       <c r="E67" t="n">
-        <v>1360</v>
+        <v>1280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2515,11 +2515,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>616</v>
+        <v>50227</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chevalerie Ogier – Continuation</t>
+          <t>Chanson de geste non identifiée (Lorrains?; fragment d'Oxford)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1306</v>
+        <v>1101</v>
       </c>
       <c r="E68" t="n">
-        <v>1315</v>
+        <v>1260</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2546,11 +2546,11 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chevalerie Vivien</t>
+          <t>Charroi de Nimes</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1181</v>
+        <v>1101</v>
       </c>
       <c r="E69" t="n">
-        <v>1220</v>
+        <v>1160</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2577,11 +2577,11 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>48936</v>
+        <v>524</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chevalier a l'espee</t>
+          <t>Chetifs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2597,22 +2597,22 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>618</v>
+        <v>721</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Chevalier au Cygne (Beatrix)</t>
+          <t>Chevalerie Ogier de Danemarche</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2621,60 +2621,60 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1181</v>
+        <v>1151</v>
       </c>
       <c r="E71" t="n">
-        <v>1200</v>
+        <v>1225</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>722</v>
+        <v>616</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chevalier au Cygne et Godefroi de Bouillon</t>
+          <t>Chevalerie Ogier – Continuation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1356</v>
+        <v>1306</v>
       </c>
       <c r="E72" t="n">
-        <v>1356</v>
+        <v>1315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>50320</v>
+        <v>617</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chevalier au cygne</t>
+          <t>Chevalerie Vivien</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2683,60 +2683,60 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1281</v>
+        <v>1181</v>
       </c>
       <c r="E73" t="n">
-        <v>1305</v>
+        <v>1220</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>49261</v>
+        <v>618</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chevalier du papegau</t>
+          <t>Chevalier au Cygne (Beatrix)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1381</v>
+        <v>1181</v>
       </c>
       <c r="E74" t="n">
-        <v>1420</v>
+        <v>1200</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>621</v>
+        <v>48829</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chrétienté Corbaran</t>
+          <t>Cleomadés</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1201</v>
+        <v>1274</v>
       </c>
       <c r="E75" t="n">
-        <v>1300</v>
+        <v>1284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2763,42 +2763,42 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>723</v>
+        <v>48747</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ciperis de Vignevaux</t>
+          <t>Cligès</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1341</v>
+        <v>1172</v>
       </c>
       <c r="E76" t="n">
-        <v>1415</v>
+        <v>1181</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>48826</v>
+        <v>535</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Claris et Laris</t>
+          <t>Conquete de Jerusalem</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2807,29 +2807,29 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1268</v>
+        <v>1181</v>
       </c>
       <c r="E77" t="n">
-        <v>1291</v>
+        <v>1200</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>619</v>
+        <v>724</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Clarisse et Florent</t>
+          <t>Couronnement de Louis</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1276</v>
+        <v>1101</v>
       </c>
       <c r="E78" t="n">
-        <v>1300</v>
+        <v>1166</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2856,23 +2856,23 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>620</v>
+        <v>757</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Clarisse et Florent</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1276</v>
+        <v>1350</v>
       </c>
       <c r="E79" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2887,11 +2887,11 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>48829</v>
+        <v>49488</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cleomadés</t>
+          <t>Departement des enfans Aimeri</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2900,122 +2900,122 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1274</v>
+        <v>1201</v>
       </c>
       <c r="E80" t="n">
-        <v>1284</v>
+        <v>1300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>48835</v>
+        <v>710</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cleomadés</t>
+          <t>Destruction de Rome</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1459</v>
+        <v>1170</v>
       </c>
       <c r="E81" t="n">
-        <v>1468</v>
+        <v>1170</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>48838</v>
+        <v>49489</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cleomadés</t>
+          <t>Dolopathos</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1401</v>
+        <v>1201</v>
       </c>
       <c r="E82" t="n">
-        <v>1500</v>
+        <v>1228</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>48848</v>
+        <v>726</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cleriadus et Meliadice</t>
+          <t>Doon de la Roche</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1431</v>
+        <v>1181</v>
       </c>
       <c r="E83" t="n">
-        <v>1450</v>
+        <v>1200</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>48747</v>
+        <v>727</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cligès</t>
+          <t>Doon de Mayence</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3024,41 +3024,41 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1172</v>
+        <v>1251</v>
       </c>
       <c r="E84" t="n">
-        <v>1181</v>
+        <v>1320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>48748</v>
+        <v>48940</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cligès</t>
+          <t>Durmart le Galois</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1455</v>
+        <v>1201</v>
       </c>
       <c r="E85" t="n">
-        <v>1455</v>
+        <v>1260</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3067,17 +3067,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>535</v>
+        <v>48741</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Conquete de Jerusalem</t>
+          <t>Erec et Enide</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3086,45 +3086,45 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1181</v>
+        <v>1166</v>
       </c>
       <c r="E86" t="n">
-        <v>1200</v>
+        <v>1175</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>50222</v>
+        <v>48945</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Conquêtes et Chroniques de Charlemagne</t>
+          <t>Escanor</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1458</v>
+        <v>1276</v>
       </c>
       <c r="E87" t="n">
-        <v>1458</v>
+        <v>1285</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3135,23 +3135,23 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>50224</v>
+        <v>642</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Conquêtes et Chroniques de Charlemagne, remaniement abrégé</t>
+          <t>Esclarmonde</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1481</v>
+        <v>1276</v>
       </c>
       <c r="E88" t="n">
-        <v>1492</v>
+        <v>1300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3166,11 +3166,11 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>49125</v>
+        <v>49768</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Conte de la charrette</t>
+          <t>Escoufle</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3179,29 +3179,29 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1301</v>
+        <v>1196</v>
       </c>
       <c r="E89" t="n">
-        <v>1320</v>
+        <v>1209</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Couronnement de Louis</t>
+          <t>Fierabras</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1101</v>
+        <v>1171</v>
       </c>
       <c r="E90" t="n">
-        <v>1166</v>
+        <v>1200</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3228,11 +3228,11 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>48864</v>
+        <v>48511</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cristal et Clarie</t>
+          <t>Floire et Blancheflor, version aristocratique</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1201</v>
+        <v>1146</v>
       </c>
       <c r="E91" t="n">
-        <v>1267</v>
+        <v>1155</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3253,29 +3253,29 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>757</v>
+        <v>647</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Floovant</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1350</v>
+        <v>1181</v>
       </c>
       <c r="E92" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3284,17 +3284,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>48906</v>
+        <v>732</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dame a la licorne et beau chevalier</t>
+          <t>Florence de Rome</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3303,14 +3303,14 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1301</v>
+        <v>1181</v>
       </c>
       <c r="E93" t="n">
-        <v>1350</v>
+        <v>1225</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3321,11 +3321,11 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>49485</v>
+        <v>48485</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Departement des enfans Aimeri</t>
+          <t>Florimont</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3334,14 +3334,14 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1176</v>
+        <v>1188</v>
       </c>
       <c r="E94" t="n">
-        <v>1225</v>
+        <v>1188</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3352,27 +3352,27 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>49488</v>
+        <v>48490</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Departement des enfans Aimeri</t>
+          <t>Florimont</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1201</v>
+        <v>1401</v>
       </c>
       <c r="E95" t="n">
-        <v>1300</v>
+        <v>1450</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3383,11 +3383,11 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>49852</v>
+        <v>49097</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Departement des fils Aimeri</t>
+          <t>Folie Lancelot</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3396,14 +3396,14 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1196</v>
+        <v>1236</v>
       </c>
       <c r="E96" t="n">
-        <v>1205</v>
+        <v>1240</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3414,11 +3414,11 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>48559</v>
+        <v>733</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deuxième continuation</t>
+          <t>Fouque de Candie</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3427,14 +3427,14 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1196</v>
+        <v>1166</v>
       </c>
       <c r="E97" t="n">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3445,11 +3445,11 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>49489</v>
+        <v>651</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dolopathos</t>
+          <t>Garin de Monglane</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3461,11 +3461,11 @@
         <v>1201</v>
       </c>
       <c r="E98" t="n">
-        <v>1228</v>
+        <v>1300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3476,11 +3476,11 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Doon de la Roche</t>
+          <t>Girart de Vienne</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3492,7 +3492,7 @@
         <v>1181</v>
       </c>
       <c r="E99" t="n">
-        <v>1200</v>
+        <v>1220</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3507,11 +3507,11 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>727</v>
+        <v>711</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Doon de Mayence</t>
+          <t>Gormont et Isembart</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1251</v>
+        <v>1068</v>
       </c>
       <c r="E100" t="n">
-        <v>1320</v>
+        <v>1130</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3538,11 +3538,11 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>48940</v>
+        <v>661</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Durmart le Galois</t>
+          <t>Gui de Bourgogne</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3551,14 +3551,14 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1201</v>
+        <v>1211</v>
       </c>
       <c r="E101" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3569,11 +3569,11 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>728</v>
+        <v>662</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Elie de Saint Gille</t>
+          <t>Gui de Nanteuil</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="E102" t="n">
-        <v>1200</v>
+        <v>1220</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>48569</v>
+        <v>50237</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Elucidation</t>
+          <t>Guiron le courtois, Continuation</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1201</v>
+        <v>1241</v>
       </c>
       <c r="E103" t="n">
-        <v>1250</v>
+        <v>1280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3631,11 +3631,11 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>48528</v>
+        <v>664</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Eneas</t>
+          <t>Hervis de Metz</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3644,14 +3644,14 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1156</v>
+        <v>1201</v>
       </c>
       <c r="E104" t="n">
-        <v>1165</v>
+        <v>1225</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3662,11 +3662,11 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>632</v>
+        <v>666</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Enfances Garin de Monglane</t>
+          <t>Huon de Bordeaux</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1280</v>
+        <v>1181</v>
       </c>
       <c r="E105" t="n">
-        <v>1320</v>
+        <v>1268</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3693,11 +3693,11 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>633</v>
+        <v>49521</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Enfances Godefroi</t>
+          <t>Kanor</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3706,29 +3706,29 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1151</v>
+        <v>1271</v>
       </c>
       <c r="E106" t="n">
-        <v>1200</v>
+        <v>1290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>634</v>
+        <v>49284</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Enfances Guillaume</t>
+          <t>Laurin, fils de Marques le Sénéchal</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3737,14 +3737,14 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1201</v>
+        <v>1256</v>
       </c>
       <c r="E107" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3755,11 +3755,11 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>729</v>
+        <v>766</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Enfances Ogier</t>
+          <t>Lohier et Malart</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1269</v>
+        <v>1301</v>
       </c>
       <c r="E108" t="n">
-        <v>1285</v>
+        <v>1350</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3786,11 +3786,11 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Enfances Vivien</t>
+          <t>Mainet</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1201</v>
+        <v>1151</v>
       </c>
       <c r="E109" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3817,11 +3817,11 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>48750</v>
+        <v>48703</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Eracle</t>
+          <t>Mainet</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3830,14 +3830,14 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1150</v>
+        <v>1201</v>
       </c>
       <c r="E110" t="n">
-        <v>1186</v>
+        <v>1220</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -3848,11 +3848,11 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>48741</v>
+        <v>675</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Erec et Enide</t>
+          <t>Maugis d'Aigremont</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3861,14 +3861,14 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1166</v>
+        <v>1201</v>
       </c>
       <c r="E111" t="n">
-        <v>1175</v>
+        <v>1266</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -3879,23 +3879,23 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>48743</v>
+        <v>49258</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Erec et Enide</t>
+          <t>Meliador</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1281</v>
+        <v>1362</v>
       </c>
       <c r="E112" t="n">
-        <v>1300</v>
+        <v>1387</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3910,23 +3910,23 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>48744</v>
+        <v>50241</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Erec et Enide</t>
+          <t>Meliadus, Continuation</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1441</v>
+        <v>1251</v>
       </c>
       <c r="E113" t="n">
-        <v>1465</v>
+        <v>1300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -3941,11 +3941,11 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>48945</v>
+        <v>48952</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Escanor</t>
+          <t>Meraugis de Portlesguez</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1276</v>
+        <v>1201</v>
       </c>
       <c r="E114" t="n">
-        <v>1285</v>
+        <v>1235</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -3972,11 +3972,11 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>642</v>
+        <v>48989</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Esclarmonde</t>
+          <t>Merlin</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3985,14 +3985,14 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1276</v>
+        <v>1191</v>
       </c>
       <c r="E115" t="n">
-        <v>1300</v>
+        <v>1205</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4003,23 +4003,23 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>643</v>
+        <v>767</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Esclarmonde</t>
+          <t>Moniage Guillaume fragm.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1351</v>
+        <v>1181</v>
       </c>
       <c r="E116" t="n">
-        <v>1400</v>
+        <v>1220</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -4034,11 +4034,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>49768</v>
+        <v>747</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Escoufle</t>
+          <t>Mort Aimeri de Narbonne</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4047,29 +4047,29 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1196</v>
+        <v>1176</v>
       </c>
       <c r="E117" t="n">
-        <v>1209</v>
+        <v>1225</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>48976</v>
+        <v>49850</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Fergus</t>
+          <t>Narbonnais / Siege de Narbonne</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4078,14 +4078,14 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="E118" t="n">
-        <v>1233</v>
+        <v>1205</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4096,11 +4096,11 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>730</v>
+        <v>635</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Fierabras</t>
+          <t>Narbonnais</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1171</v>
+        <v>1201</v>
       </c>
       <c r="E119" t="n">
-        <v>1200</v>
+        <v>1220</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4127,11 +4127,11 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>48717</v>
+        <v>48673</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Fierabras</t>
+          <t>Othovien</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4140,10 +4140,10 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1461</v>
+        <v>1454</v>
       </c>
       <c r="E120" t="n">
-        <v>1470</v>
+        <v>1454</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -4152,29 +4152,29 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>48716</v>
+        <v>731</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Fierabras</t>
+          <t>Otinel</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1381</v>
+        <v>1151</v>
       </c>
       <c r="E121" t="n">
-        <v>1400</v>
+        <v>1250</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -4189,42 +4189,42 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>49255</v>
+        <v>48806</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fils du roi Constant</t>
+          <t>Paris et Vienne</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1290</v>
+        <v>1432</v>
       </c>
       <c r="E122" t="n">
-        <v>1298</v>
+        <v>1432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>48511</v>
+        <v>49519</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Floire et Blancheflor, version aristocratique</t>
+          <t>Pelyarmenus</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4233,45 +4233,45 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1146</v>
+        <v>1279</v>
       </c>
       <c r="E123" t="n">
-        <v>1155</v>
+        <v>1288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>48513</v>
+        <v>49252</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Floire et Blancheflor, version dite populaire</t>
+          <t>Perceforest</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1181</v>
+        <v>1441</v>
       </c>
       <c r="E124" t="n">
-        <v>1200</v>
+        <v>1460</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4282,11 +4282,11 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>647</v>
+        <v>48551</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Floovant</t>
+          <t>Perceval ou le Conte du Graal</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4295,45 +4295,45 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="E125" t="n">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>732</v>
+        <v>48764</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Florence de Rome</t>
+          <t>Pontus et Sidoine</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1181</v>
+        <v>1381</v>
       </c>
       <c r="E126" t="n">
-        <v>1225</v>
+        <v>1450</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4344,54 +4344,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>557</v>
+        <v>48554</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Florence de Rome</t>
+          <t>Première continuation, dite Continuation Gauvain</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1301</v>
+        <v>1181</v>
       </c>
       <c r="E127" t="n">
-        <v>1400</v>
+        <v>1205</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>913</v>
+        <v>646</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Florent et Octavien</t>
+          <t>Raoul de Cambrai</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1301</v>
+        <v>1176</v>
       </c>
       <c r="E128" t="n">
-        <v>1400</v>
+        <v>1220</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -4400,29 +4400,29 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>914</v>
+        <v>753</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Florent et Octavien</t>
+          <t>Reine Sébile</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1352</v>
+        <v>1246</v>
       </c>
       <c r="E129" t="n">
-        <v>1361</v>
+        <v>1255</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -4431,17 +4431,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>48721</v>
+        <v>48386</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Floriant et Florete</t>
+          <t>Siege d'Orange</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4450,60 +4450,60 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1226</v>
+        <v>1161</v>
       </c>
       <c r="E130" t="n">
-        <v>1300</v>
+        <v>1180</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>48722</v>
+        <v>691</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Floriant et Florete</t>
+          <t>Siege de Barbastre</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1476</v>
+        <v>1150</v>
       </c>
       <c r="E131" t="n">
-        <v>1485</v>
+        <v>1220</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>48485</v>
+        <v>50238</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Florimont</t>
+          <t>Suite Guiron</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4512,14 +4512,14 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1188</v>
+        <v>1241</v>
       </c>
       <c r="E132" t="n">
-        <v>1188</v>
+        <v>1270</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4530,27 +4530,27 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>48488</v>
+        <v>49086</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Florimont</t>
+          <t>Suite Post-Vulgate du Merlin</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1419</v>
+        <v>1236</v>
       </c>
       <c r="E133" t="n">
-        <v>1428</v>
+        <v>1245</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -4561,54 +4561,54 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>48489</v>
+        <v>771</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Florimont</t>
+          <t>Syracon</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1451</v>
+        <v>1180</v>
       </c>
       <c r="E134" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>48490</v>
+        <v>48537</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Florimont</t>
+          <t>Thèbes</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1401</v>
+        <v>1146</v>
       </c>
       <c r="E135" t="n">
-        <v>1450</v>
+        <v>1162</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4623,11 +4623,11 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>48726</v>
+        <v>48521</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Floris et Lyriopé</t>
+          <t>Troie, prose 3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1234</v>
+        <v>1281</v>
       </c>
       <c r="E136" t="n">
-        <v>1266</v>
+        <v>1300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -4654,11 +4654,11 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>49097</v>
+        <v>48691</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Folie Lancelot</t>
+          <t>Vengeance Raguidel</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1236</v>
+        <v>1196</v>
       </c>
       <c r="E137" t="n">
-        <v>1240</v>
+        <v>1225</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -4685,11 +4685,11 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>733</v>
+        <v>48523</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Fouque de Candie</t>
+          <t>Troie, prose 5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4698,14 +4698,14 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1166</v>
+        <v>1301</v>
       </c>
       <c r="E138" t="n">
-        <v>1220</v>
+        <v>1320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -4716,11 +4716,11 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>734</v>
+        <v>696</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Gaidon</t>
+          <t>Vivien de Monbranc</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1218</v>
+        <v>1200</v>
       </c>
       <c r="E139" t="n">
-        <v>1240</v>
+        <v>1320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -4747,11 +4747,11 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>49905</v>
+        <v>606</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Galeran de Bretagne</t>
+          <t>Bueve de Hanstonne cont. 2</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1181</v>
+        <v>1221</v>
       </c>
       <c r="E140" t="n">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -4772,17 +4772,17 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>579</v>
+        <v>48705</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Galien (li Restorés)</t>
+          <t>Huon de Bordeaux</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4809,27 +4809,27 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>48699</v>
+        <v>48765</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Galien le restoré</t>
+          <t>Yvain ou le chevalier au lion</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1401</v>
+        <v>1173</v>
       </c>
       <c r="E142" t="n">
-        <v>1500</v>
+        <v>1186</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -4840,11 +4840,11 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>651</v>
+        <v>48859</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Garin de Monglane</t>
+          <t>Comte d'Anjou</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4853,45 +4853,45 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1201</v>
+        <v>1314</v>
       </c>
       <c r="E143" t="n">
-        <v>1300</v>
+        <v>1316</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>48700</v>
+        <v>48960</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Garin de Monglane</t>
+          <t>Merveilles de Rigomer</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1459</v>
+        <v>1241</v>
       </c>
       <c r="E144" t="n">
-        <v>1520</v>
+        <v>1260</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -4902,11 +4902,11 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>652</v>
+        <v>50316</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Garin le Lorrain</t>
+          <t>Naissance du chevalier au cygne Elioxe-Beatrix (version hybride)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4918,7 +4918,7 @@
         <v>1181</v>
       </c>
       <c r="E145" t="n">
-        <v>1200</v>
+        <v>1220</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -4927,33 +4927,33 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>48678</v>
+        <v>48572</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Garin le lorrain</t>
+          <t>Perceval</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1467</v>
+        <v>1196</v>
       </c>
       <c r="E146" t="n">
-        <v>1500</v>
+        <v>1210</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -4964,11 +4964,11 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>653</v>
+        <v>49785</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Gaufrey</t>
+          <t>Abladane</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4977,14 +4977,14 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1201</v>
+        <v>1256</v>
       </c>
       <c r="E147" t="n">
-        <v>1300</v>
+        <v>1293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -4995,27 +4995,27 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>49761</v>
+        <v>623</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Gérard de Nevers</t>
+          <t>Aiol</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1451</v>
+        <v>1201</v>
       </c>
       <c r="E148" t="n">
-        <v>1464</v>
+        <v>1220</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5026,27 +5026,27 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>49882</v>
+        <v>48501</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Gerbert de Metz</t>
+          <t>Alexandre en Orient</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1401</v>
+        <v>1165</v>
       </c>
       <c r="E149" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5057,11 +5057,11 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>658</v>
+        <v>48500</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Girart de Roussillon</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5070,14 +5070,14 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1326</v>
+        <v>1156</v>
       </c>
       <c r="E150" t="n">
-        <v>1348</v>
+        <v>1165</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5088,23 +5088,23 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>49888</v>
+        <v>588</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Girart de Roussillon</t>
+          <t>Ami et Amile</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1447</v>
+        <v>1196</v>
       </c>
       <c r="E151" t="n">
-        <v>1447</v>
+        <v>1220</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -5119,11 +5119,11 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>736</v>
+        <v>48581</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Girart de Vienne</t>
+          <t>Ami et Amile</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1181</v>
+        <v>1301</v>
       </c>
       <c r="E152" t="n">
-        <v>1220</v>
+        <v>1400</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -5150,11 +5150,11 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Girart de Vienne</t>
+          <t>Ami et Amile</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1351</v>
+        <v>1381</v>
       </c>
       <c r="E153" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -5181,23 +5181,23 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>654</v>
+        <v>47611</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Girbert de Metz</t>
+          <t>Anséis de Metz</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1181</v>
+        <v>1467</v>
       </c>
       <c r="E154" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -5212,11 +5212,11 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>48964</v>
+        <v>598</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Gliglois</t>
+          <t>Auberon</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5225,14 +5225,14 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1201</v>
+        <v>1261</v>
       </c>
       <c r="E155" t="n">
-        <v>1250</v>
+        <v>1311</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5243,11 +5243,11 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>661</v>
+        <v>513</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Gui de Bourgogne</t>
+          <t>Audigier</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5256,10 +5256,10 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1211</v>
+        <v>1181</v>
       </c>
       <c r="E156" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -5268,17 +5268,17 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>662</v>
+        <v>709</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Gui de Nanteuil</t>
+          <t>Bataille Loquifer</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1180</v>
+        <v>1166</v>
       </c>
       <c r="E157" t="n">
         <v>1220</v>
@@ -5305,23 +5305,23 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>48693</v>
+        <v>720</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Gui de Warwick</t>
+          <t>Bâtard de Bouillon</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1441</v>
+        <v>1301</v>
       </c>
       <c r="E158" t="n">
-        <v>1445</v>
+        <v>1355</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -5330,17 +5330,17 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>737</v>
+        <v>599</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Guibert d'Andrenas</t>
+          <t>Baudouin de Sebourc</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5349,45 +5349,45 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1181</v>
+        <v>1314</v>
       </c>
       <c r="E159" t="n">
-        <v>1224</v>
+        <v>1350</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>50146</v>
+        <v>47644</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Guillaume d'Angleterre</t>
+          <t>Belle Hélène de Constantinople</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1181</v>
+        <v>1448</v>
       </c>
       <c r="E160" t="n">
-        <v>1220</v>
+        <v>1448</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -5398,11 +5398,11 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>47641</v>
+        <v>48467</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Guillaume d'Orange en prose</t>
+          <t>Blancandin</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5411,60 +5411,60 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1454</v>
+        <v>1463</v>
       </c>
       <c r="E161" t="n">
-        <v>1456</v>
+        <v>1472</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>50233</v>
+        <v>48466</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Guiron le courtois</t>
+          <t>Blancandin</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1236</v>
+        <v>1460</v>
       </c>
       <c r="E162" t="n">
-        <v>1240</v>
+        <v>1469</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>49517</v>
+        <v>48568</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Helcanus</t>
+          <t>Bliocadran</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5473,14 +5473,14 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1281</v>
+        <v>1201</v>
       </c>
       <c r="E163" t="n">
-        <v>1290</v>
+        <v>1300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -5491,11 +5491,11 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>765</v>
+        <v>604</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Hernaut de Beaulande</t>
+          <t>Brun de la Montagne</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5516,17 +5516,17 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>664</v>
+        <v>689</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Hervis de Metz</t>
+          <t>Bueve de Commarchis</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1201</v>
+        <v>1272</v>
       </c>
       <c r="E165" t="n">
-        <v>1225</v>
+        <v>1300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -5553,27 +5553,27 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>48676</v>
+        <v>605</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>histoire de la reine Berthe et du roy Pepin</t>
+          <t>Bueve de Hanstonne cont. 1</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1401</v>
+        <v>1200</v>
       </c>
       <c r="E166" t="n">
-        <v>1500</v>
+        <v>1225</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -5584,11 +5584,11 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>740</v>
+        <v>48462</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Hugues Capet</t>
+          <t>Bueve de Hanstonne</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5597,14 +5597,14 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1354</v>
+        <v>1460</v>
       </c>
       <c r="E167" t="n">
-        <v>1365</v>
+        <v>1469</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -5615,42 +5615,42 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>666</v>
+        <v>48735</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Huon de Bordeaux</t>
+          <t>Cardenois et Passebeauté</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1181</v>
+        <v>1376</v>
       </c>
       <c r="E168" t="n">
-        <v>1268</v>
+        <v>1400</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>665</v>
+        <v>47608</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Huon de Bordeaux</t>
+          <t>Charlemagne et Anseïs</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5659,10 +5659,10 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1216</v>
+        <v>1401</v>
       </c>
       <c r="E169" t="n">
-        <v>1420</v>
+        <v>1500</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -5677,23 +5677,23 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>48666</v>
+        <v>718</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Huon de Bordeaux</t>
+          <t>Charlemagne</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1455</v>
+        <v>1296</v>
       </c>
       <c r="E170" t="n">
-        <v>1455</v>
+        <v>1314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -5708,54 +5708,54 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>48755</v>
+        <v>719</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ille et Galeron</t>
+          <t>Charles le Chauve</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1151</v>
+        <v>1355</v>
       </c>
       <c r="E171" t="n">
-        <v>1180</v>
+        <v>1380</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>50192</v>
+        <v>48471</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Istoire de la Chastelaine du Vergier et de Tristan le Chevalier</t>
+          <t>Chastelain de Coucy</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1401</v>
+        <v>1281</v>
       </c>
       <c r="E172" t="n">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -5770,42 +5770,42 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>671</v>
+        <v>48473</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Jehan de Lanson</t>
+          <t>Chastelain de Coucy</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1201</v>
+        <v>1459</v>
       </c>
       <c r="E173" t="n">
-        <v>1233</v>
+        <v>1468</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>49866</v>
+        <v>615</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Jehan et Blonde</t>
+          <t>Chevalerie Ogier en alexandrins</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5814,29 +5814,29 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1226</v>
+        <v>1328</v>
       </c>
       <c r="E174" t="n">
-        <v>1245</v>
+        <v>1360</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>48987</v>
+        <v>48936</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Joseph d'Arimathie ou Estoire del saint Graal</t>
+          <t>Chevalier a l'espee</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1191</v>
+        <v>1181</v>
       </c>
       <c r="E175" t="n">
-        <v>1201</v>
+        <v>1220</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -5863,42 +5863,42 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>49006</v>
+        <v>722</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Joseph d'Arimathie Vulgate ou Estoire del Saint Graal</t>
+          <t>Chevalier au Cygne et Godefroi de Bouillon</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1215</v>
+        <v>1356</v>
       </c>
       <c r="E176" t="n">
-        <v>1235</v>
+        <v>1356</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>672</v>
+        <v>50320</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Jourdain de Blaye ou Blaive</t>
+          <t>Chevalier au cygne</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5907,29 +5907,29 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1181</v>
+        <v>1281</v>
       </c>
       <c r="E177" t="n">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>673</v>
+        <v>49261</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Jourdain de Blaye ou Blaive</t>
+          <t>Chevalier du papegau</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5938,14 +5938,14 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1401</v>
+        <v>1381</v>
       </c>
       <c r="E178" t="n">
-        <v>1455</v>
+        <v>1420</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -5956,73 +5956,73 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>48707</v>
+        <v>621</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jourdain de Blaye</t>
+          <t>Chrétienté Corbaran</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1456</v>
+        <v>1201</v>
       </c>
       <c r="E179" t="n">
-        <v>1456</v>
+        <v>1300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>49521</v>
+        <v>723</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kanor</t>
+          <t>Ciperis de Vignevaux</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1271</v>
+        <v>1341</v>
       </c>
       <c r="E180" t="n">
-        <v>1290</v>
+        <v>1415</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>48814</v>
+        <v>48826</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>L'âtre périlleux</t>
+          <t>Claris et Laris</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1251</v>
+        <v>1268</v>
       </c>
       <c r="E181" t="n">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -6049,11 +6049,11 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>49102</v>
+        <v>619</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Lancelot</t>
+          <t>Clarisse et Florent</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6062,14 +6062,14 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1173</v>
+        <v>1276</v>
       </c>
       <c r="E182" t="n">
-        <v>1182</v>
+        <v>1300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6080,11 +6080,11 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>49284</v>
+        <v>620</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Laurin, fils de Marques le Sénéchal</t>
+          <t>Clarisse et Florent</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6093,14 +6093,14 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1256</v>
+        <v>1276</v>
       </c>
       <c r="E183" t="n">
         <v>1300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -6111,42 +6111,42 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>741</v>
+        <v>48835</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Lion de Bourges en alexandrins</t>
+          <t>Cleomadés</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1301</v>
+        <v>1459</v>
       </c>
       <c r="E184" t="n">
-        <v>1400</v>
+        <v>1468</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>624</v>
+        <v>48838</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Lion de Bourges en octosyllabes</t>
+          <t>Cleomadés</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6155,91 +6155,91 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1351</v>
+        <v>1401</v>
       </c>
       <c r="E185" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>49093</v>
+        <v>48848</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Livre d'Artus</t>
+          <t>Cleriadus et Meliadice</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1226</v>
+        <v>1431</v>
       </c>
       <c r="E186" t="n">
-        <v>1250</v>
+        <v>1450</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>49863</v>
+        <v>48748</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Manekine</t>
+          <t>Cligès</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1231</v>
+        <v>1455</v>
       </c>
       <c r="E187" t="n">
-        <v>1265</v>
+        <v>1455</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>49865</v>
+        <v>50222</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Manekine</t>
+          <t>Conquêtes et Chroniques de Charlemagne</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6248,45 +6248,45 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1441</v>
+        <v>1458</v>
       </c>
       <c r="E188" t="n">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>49513</v>
+        <v>50224</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Marques de Rome</t>
+          <t>Conquêtes et Chroniques de Charlemagne, remaniement abrégé</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1251</v>
+        <v>1481</v>
       </c>
       <c r="E189" t="n">
-        <v>1277</v>
+        <v>1492</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -6297,11 +6297,11 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>675</v>
+        <v>49125</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Maugis d'Aigremont</t>
+          <t>Conte de la charrette</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6310,14 +6310,14 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1201</v>
+        <v>1301</v>
       </c>
       <c r="E190" t="n">
-        <v>1266</v>
+        <v>1320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -6328,11 +6328,11 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>48947</v>
+        <v>48864</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Meliacin</t>
+          <t>Cristal et Clarie</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6341,60 +6341,60 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1276</v>
+        <v>1201</v>
       </c>
       <c r="E191" t="n">
-        <v>1294</v>
+        <v>1267</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>49258</v>
+        <v>48906</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Meliador</t>
+          <t>Dame a la licorne et beau chevalier</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1362</v>
+        <v>1301</v>
       </c>
       <c r="E192" t="n">
-        <v>1387</v>
+        <v>1350</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>50241</v>
+        <v>49485</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Meliadus, Continuation</t>
+          <t>Departement des enfans Aimeri</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6403,14 +6403,14 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1251</v>
+        <v>1176</v>
       </c>
       <c r="E193" t="n">
-        <v>1300</v>
+        <v>1225</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -6421,73 +6421,73 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>48811</v>
+        <v>49852</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Melusine</t>
+          <t>Departement des fils Aimeri</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1396</v>
+        <v>1196</v>
       </c>
       <c r="E194" t="n">
-        <v>1410</v>
+        <v>1205</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>48808</v>
+        <v>48559</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Mélusine</t>
+          <t>Deuxième continuation</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1392</v>
+        <v>1196</v>
       </c>
       <c r="E195" t="n">
-        <v>1393</v>
+        <v>1215</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>48952</v>
+        <v>728</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Meraugis de Portlesguez</t>
+          <t>Elie de Saint Gille</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6496,29 +6496,29 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1201</v>
+        <v>1181</v>
       </c>
       <c r="E196" t="n">
-        <v>1235</v>
+        <v>1200</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>48938</v>
+        <v>48569</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Mériadeuc ou le chevalier aux deux épées</t>
+          <t>Elucidation</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6545,11 +6545,11 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>743</v>
+        <v>48528</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Moniage Guillaume, 1re rédaction (courte)</t>
+          <t>Eneas</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6558,14 +6558,14 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1134</v>
+        <v>1156</v>
       </c>
       <c r="E198" t="n">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -6576,11 +6576,11 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>744</v>
+        <v>632</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Moniage Guillaume, 2e rédaction (longue)</t>
+          <t>Enfances Garin de Monglane</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1171</v>
+        <v>1280</v>
       </c>
       <c r="E199" t="n">
-        <v>1190</v>
+        <v>1320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -6607,11 +6607,11 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>745</v>
+        <v>633</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Moniage Rainouart</t>
+          <t>Enfances Godefroi</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6620,29 +6620,29 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1171</v>
+        <v>1151</v>
       </c>
       <c r="E200" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>747</v>
+        <v>634</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Mort Aimeri de Narbonne</t>
+          <t>Enfances Guillaume</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1176</v>
+        <v>1201</v>
       </c>
       <c r="E201" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -6669,11 +6669,11 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>644</v>
+        <v>729</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Mort de Maugis</t>
+          <t>Enfances Ogier</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6682,10 +6682,10 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1201</v>
+        <v>1269</v>
       </c>
       <c r="E202" t="n">
-        <v>1300</v>
+        <v>1285</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -6700,11 +6700,11 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>48954</v>
+        <v>640</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Mule sans frein</t>
+          <t>Enfances Vivien</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6713,14 +6713,14 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1181</v>
+        <v>1201</v>
       </c>
       <c r="E203" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -6731,11 +6731,11 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>677</v>
+        <v>48743</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Naissance du chevalier au cygne Beatrix</t>
+          <t>Erec et Enide</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6744,41 +6744,41 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1181</v>
+        <v>1281</v>
       </c>
       <c r="E204" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>676</v>
+        <v>643</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Naissance du chevalier au cygne Elioxe</t>
+          <t>Esclarmonde</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1181</v>
+        <v>1351</v>
       </c>
       <c r="E205" t="n">
-        <v>1220</v>
+        <v>1400</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -6787,17 +6787,17 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>635</v>
+        <v>48976</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Narbonnais</t>
+          <t>Fergus</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6809,11 +6809,11 @@
         <v>1201</v>
       </c>
       <c r="E206" t="n">
-        <v>1220</v>
+        <v>1233</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -6824,23 +6824,23 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>648</v>
+        <v>48717</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Octavian</t>
+          <t>Fierabras</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1281</v>
+        <v>1461</v>
       </c>
       <c r="E207" t="n">
-        <v>1320</v>
+        <v>1470</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -6849,17 +6849,17 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>48840</v>
+        <v>48716</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Olivier de Castille et Artus d'Algarbe</t>
+          <t>Fierabras</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6868,29 +6868,29 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1431</v>
+        <v>1381</v>
       </c>
       <c r="E208" t="n">
-        <v>1466</v>
+        <v>1400</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>680</v>
+        <v>49255</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Orson de Beauvais</t>
+          <t>Fils du roi Constant</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6899,14 +6899,14 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1176</v>
+        <v>1290</v>
       </c>
       <c r="E209" t="n">
-        <v>1225</v>
+        <v>1298</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -6917,42 +6917,42 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>48673</v>
+        <v>48513</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Othovien</t>
+          <t>Floire et Blancheflor, version dite populaire</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1454</v>
+        <v>1181</v>
       </c>
       <c r="E210" t="n">
-        <v>1454</v>
+        <v>1200</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>48806</v>
+        <v>557</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Paris et Vienne</t>
+          <t>Florence de Rome</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6961,14 +6961,14 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1432</v>
+        <v>1301</v>
       </c>
       <c r="E211" t="n">
-        <v>1432</v>
+        <v>1400</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -6979,23 +6979,23 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>681</v>
+        <v>913</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Parise la Duchesse</t>
+          <t>Florent et Octavien</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1196</v>
+        <v>1301</v>
       </c>
       <c r="E212" t="n">
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -7004,48 +7004,48 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>48477</v>
+        <v>914</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Parthonopeus de Blois</t>
+          <t>Florent et Octavien</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1176</v>
+        <v>1352</v>
       </c>
       <c r="E213" t="n">
-        <v>1188</v>
+        <v>1361</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>682</v>
+        <v>48721</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Pélerinage de Charlemagne</t>
+          <t>Floriant et Florete</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7054,60 +7054,60 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1150</v>
+        <v>1226</v>
       </c>
       <c r="E214" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>49519</v>
+        <v>48722</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Pelyarmenus</t>
+          <t>Floriant et Florete</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1279</v>
+        <v>1476</v>
       </c>
       <c r="E215" t="n">
-        <v>1288</v>
+        <v>1485</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>49252</v>
+        <v>48488</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Perceforest</t>
+          <t>Florimont</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7116,45 +7116,45 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1441</v>
+        <v>1419</v>
       </c>
       <c r="E216" t="n">
-        <v>1460</v>
+        <v>1428</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>48551</v>
+        <v>48489</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Perceval ou le Conte du Graal</t>
+          <t>Florimont</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1182</v>
+        <v>1451</v>
       </c>
       <c r="E217" t="n">
-        <v>1189</v>
+        <v>1500</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -7165,42 +7165,42 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>48764</v>
+        <v>48726</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Pontus et Sidoine</t>
+          <t>Floris et Lyriopé</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1381</v>
+        <v>1234</v>
       </c>
       <c r="E218" t="n">
-        <v>1450</v>
+        <v>1266</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>48554</v>
+        <v>734</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Première continuation, dite Continuation Gauvain</t>
+          <t>Gaidon</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7209,14 +7209,14 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1181</v>
+        <v>1218</v>
       </c>
       <c r="E219" t="n">
-        <v>1205</v>
+        <v>1240</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -7227,11 +7227,11 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>749</v>
+        <v>49905</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Prise d' Orange</t>
+          <t>Galeran de Bretagne</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7240,29 +7240,29 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1161</v>
+        <v>1181</v>
       </c>
       <c r="E220" t="n">
         <v>1220</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>49141</v>
+        <v>579</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Propheties de Merlin</t>
+          <t>Galien (li Restorés)</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7271,14 +7271,14 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1267</v>
+        <v>1201</v>
       </c>
       <c r="E221" t="n">
         <v>1300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -7289,27 +7289,27 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>48565</v>
+        <v>48699</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Quatrième continuation</t>
+          <t>Galien le restoré</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1226</v>
+        <v>1401</v>
       </c>
       <c r="E222" t="n">
-        <v>1230</v>
+        <v>1500</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -7320,23 +7320,23 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>646</v>
+        <v>48700</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Raoul de Cambrai</t>
+          <t>Garin de Monglane</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1176</v>
+        <v>1459</v>
       </c>
       <c r="E223" t="n">
-        <v>1220</v>
+        <v>1520</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -7351,42 +7351,42 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>49827</v>
+        <v>48678</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Reinbert</t>
+          <t>Garin le lorrain</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1201</v>
+        <v>1467</v>
       </c>
       <c r="E224" t="n">
-        <v>1267</v>
+        <v>1500</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Renaut de Montauban</t>
+          <t>Gaufrey</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1181</v>
+        <v>1201</v>
       </c>
       <c r="E225" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -7413,11 +7413,11 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>685</v>
+        <v>49761</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Renaut de Montauban</t>
+          <t>Gérard de Nevers</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7426,29 +7426,29 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1401</v>
+        <v>1451</v>
       </c>
       <c r="E226" t="n">
-        <v>1445</v>
+        <v>1464</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>49807</v>
+        <v>49882</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Renaut de Montauban, 1re version, 'Vulgate</t>
+          <t>Gerbert de Metz</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7460,7 +7460,7 @@
         <v>1401</v>
       </c>
       <c r="E227" t="n">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -7475,23 +7475,23 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>49820</v>
+        <v>658</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Renaut de Montauban, 2e version ('bourguignonne')</t>
+          <t>Girart de Roussillon</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1462</v>
+        <v>1326</v>
       </c>
       <c r="E228" t="n">
-        <v>1462</v>
+        <v>1348</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -7506,11 +7506,11 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>49815</v>
+        <v>49888</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Renaut de Montauban, abrégé</t>
+          <t>Girart de Roussillon</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7519,10 +7519,10 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1401</v>
+        <v>1447</v>
       </c>
       <c r="E229" t="n">
-        <v>1500</v>
+        <v>1447</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -7537,11 +7537,11 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>758</v>
+        <v>590</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Renier de Gennes</t>
+          <t>Girart de Vienne</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7562,17 +7562,17 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>703</v>
+        <v>48964</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Retour de Cornumaran</t>
+          <t>Gliglois</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7581,45 +7581,45 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1151</v>
+        <v>1201</v>
       </c>
       <c r="E231" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>773</v>
+        <v>48693</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Gui de Warwick</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1280</v>
+        <v>1441</v>
       </c>
       <c r="E232" t="n">
-        <v>1320</v>
+        <v>1445</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -7630,11 +7630,11 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>606</v>
+        <v>737</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Bueve de Hanstonne cont. 2</t>
+          <t>Guibert d'Andrenas</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7643,14 +7643,14 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1221</v>
+        <v>1181</v>
       </c>
       <c r="E233" t="n">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -7661,11 +7661,11 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>50323</v>
+        <v>50146</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Couronnement de Louis, rédaction D (courte / archaïque)</t>
+          <t>Guillaume d'Angleterre</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7674,60 +7674,60 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1101</v>
+        <v>1181</v>
       </c>
       <c r="E234" t="n">
-        <v>1250</v>
+        <v>1220</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>48546</v>
+        <v>47641</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Richars li biaus</t>
+          <t>Guillaume d'Orange en prose</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1251</v>
+        <v>1454</v>
       </c>
       <c r="E235" t="n">
-        <v>1300</v>
+        <v>1456</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>690</v>
+        <v>49517</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Roland</t>
+          <t>Helcanus</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7736,14 +7736,14 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1086</v>
+        <v>1281</v>
       </c>
       <c r="E236" t="n">
-        <v>1105</v>
+        <v>1290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -7754,23 +7754,23 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>48783</v>
+        <v>765</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Roland</t>
+          <t>Hernaut de Beaulande</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1196</v>
+        <v>1351</v>
       </c>
       <c r="E237" t="n">
-        <v>1205</v>
+        <v>1400</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -7785,85 +7785,85 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>49777</v>
+        <v>48676</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Roman de la Rose ou Guillaume de Dole</t>
+          <t>histoire de la reine Berthe et du roy Pepin</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1201</v>
+        <v>1401</v>
       </c>
       <c r="E238" t="n">
-        <v>1232</v>
+        <v>1500</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>49753</v>
+        <v>740</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Roman de la Violette ou Gérard de Nevers</t>
+          <t>Hugues Capet</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1223</v>
+        <v>1354</v>
       </c>
       <c r="E239" t="n">
-        <v>1232</v>
+        <v>1365</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>752</v>
+        <v>665</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Saisnes</t>
+          <t>Huon de Bordeaux</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1181</v>
+        <v>1216</v>
       </c>
       <c r="E240" t="n">
-        <v>1202</v>
+        <v>1420</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -7878,27 +7878,27 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>49292</v>
+        <v>48666</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Sept Sages de Rome, version A</t>
+          <t>Huon de Bordeaux</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1201</v>
+        <v>1455</v>
       </c>
       <c r="E241" t="n">
-        <v>1278</v>
+        <v>1455</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -7909,11 +7909,11 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>49420</v>
+        <v>48755</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Sept Sages de Rome, Version A/L</t>
+          <t>Ille et Galeron</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7922,60 +7922,60 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1201</v>
+        <v>1151</v>
       </c>
       <c r="E242" t="n">
-        <v>1300</v>
+        <v>1180</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>49289</v>
+        <v>50192</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Sept Sages de Rome, version K</t>
+          <t>Istoire de la Chastelaine du Vergier et de Tristan le Chevalier</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1155</v>
+        <v>1401</v>
       </c>
       <c r="E243" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>49419</v>
+        <v>49866</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Sept Sages de Rome, Version L</t>
+          <t>Jehan et Blonde</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7984,29 +7984,29 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1201</v>
+        <v>1226</v>
       </c>
       <c r="E244" t="n">
-        <v>1233</v>
+        <v>1245</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>49483</v>
+        <v>48987</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Sept Sages de Rome, Version M</t>
+          <t>Joseph d'Arimathie ou Estoire del saint Graal</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8015,14 +8015,14 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1281</v>
+        <v>1191</v>
       </c>
       <c r="E245" t="n">
-        <v>1320</v>
+        <v>1201</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -8033,27 +8033,27 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>49291</v>
+        <v>672</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Sept Sages, version D</t>
+          <t>Jourdain de Blaye ou Blaive</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1401</v>
+        <v>1181</v>
       </c>
       <c r="E246" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -8064,23 +8064,23 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>691</v>
+        <v>673</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Siege de Barbastre</t>
+          <t>Jourdain de Blaye ou Blaive</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1150</v>
+        <v>1401</v>
       </c>
       <c r="E247" t="n">
-        <v>1220</v>
+        <v>1455</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -8095,27 +8095,27 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>48982</v>
+        <v>48707</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Silence</t>
+          <t>Jourdain de Blaye</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1251</v>
+        <v>1456</v>
       </c>
       <c r="E248" t="n">
-        <v>1300</v>
+        <v>1456</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -8126,11 +8126,11 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>692</v>
+        <v>48814</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Simon de Pouille</t>
+          <t>L'âtre périlleux</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8139,14 +8139,14 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1201</v>
+        <v>1251</v>
       </c>
       <c r="E249" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -8157,11 +8157,11 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>49086</v>
+        <v>741</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Suite Post-Vulgate du Merlin</t>
+          <t>Lion de Bourges en alexandrins</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8170,14 +8170,14 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1236</v>
+        <v>1301</v>
       </c>
       <c r="E250" t="n">
-        <v>1245</v>
+        <v>1400</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -8188,27 +8188,27 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>49088</v>
+        <v>624</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Suite Vulgate du Merlin</t>
+          <t>Lion de Bourges en octosyllabes</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1231</v>
+        <v>1351</v>
       </c>
       <c r="E251" t="n">
-        <v>1235</v>
+        <v>1400</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -8219,11 +8219,11 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>48537</v>
+        <v>49093</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Thèbes</t>
+          <t>Livre d'Artus</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8232,14 +8232,14 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1146</v>
+        <v>1226</v>
       </c>
       <c r="E252" t="n">
-        <v>1162</v>
+        <v>1250</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -8250,27 +8250,27 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>701</v>
+        <v>49863</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Theseus de Cologne</t>
+          <t>Manekine</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1361</v>
+        <v>1231</v>
       </c>
       <c r="E253" t="n">
-        <v>1378</v>
+        <v>1265</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -8281,11 +8281,11 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>48541</v>
+        <v>49865</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Theseus de Cologne, version abrégée</t>
+          <t>Manekine</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8294,14 +8294,14 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1401</v>
+        <v>1441</v>
       </c>
       <c r="E254" t="n">
-        <v>1500</v>
+        <v>1452</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -8312,11 +8312,11 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>694</v>
+        <v>48938</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Tristan de Nanteuil</t>
+          <t>Mériadeuc ou le chevalier aux deux épées</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8325,29 +8325,29 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1301</v>
+        <v>1201</v>
       </c>
       <c r="E255" t="n">
-        <v>1380</v>
+        <v>1250</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>48516</v>
+        <v>743</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Troie</t>
+          <t>Moniage Guillaume, 1re rédaction (courte)</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8356,14 +8356,14 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1161</v>
+        <v>1134</v>
       </c>
       <c r="E256" t="n">
         <v>1170</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -8374,11 +8374,11 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>48518</v>
+        <v>745</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Troie, prose 1</t>
+          <t>Moniage Rainouart</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8387,14 +8387,14 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1274</v>
+        <v>1171</v>
       </c>
       <c r="E257" t="n">
-        <v>1287</v>
+        <v>1300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -8405,11 +8405,11 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>48520</v>
+        <v>644</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Troie, prose 2</t>
+          <t>Mort de Maugis</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8418,14 +8418,14 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1281</v>
+        <v>1201</v>
       </c>
       <c r="E258" t="n">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -8436,11 +8436,11 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>48521</v>
+        <v>48954</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Troie, prose 3</t>
+          <t>Mule sans frein</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8449,14 +8449,14 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1281</v>
+        <v>1181</v>
       </c>
       <c r="E259" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -8467,11 +8467,11 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>48522</v>
+        <v>676</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Troie, prose 4</t>
+          <t>Naissance du chevalier au cygne Elioxe</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8480,91 +8480,91 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1281</v>
+        <v>1181</v>
       </c>
       <c r="E260" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>48519</v>
+        <v>648</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Troise, prose 1 remaniée</t>
+          <t>Octavian</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1401</v>
+        <v>1281</v>
       </c>
       <c r="E261" t="n">
-        <v>1500</v>
+        <v>1320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>48562</v>
+        <v>48840</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Troisième continuation</t>
+          <t>Olivier de Castille et Artus d'Algarbe</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1201</v>
+        <v>1431</v>
       </c>
       <c r="E262" t="n">
-        <v>1237</v>
+        <v>1466</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>48691</v>
+        <v>680</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Vengeance Raguidel</t>
+          <t>Orson de Beauvais</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8573,14 +8573,14 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1196</v>
+        <v>1176</v>
       </c>
       <c r="E263" t="n">
         <v>1225</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -8591,11 +8591,11 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Venjance Nostre Seigneur</t>
+          <t>Parise la Duchesse</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8604,29 +8604,29 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1181</v>
+        <v>1196</v>
       </c>
       <c r="E264" t="n">
-        <v>1220</v>
+        <v>1250</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>48770</v>
+        <v>682</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Wistasse le moine</t>
+          <t>Pélerinage de Charlemagne</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8635,29 +8635,29 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1201</v>
+        <v>1150</v>
       </c>
       <c r="E265" t="n">
-        <v>1284</v>
+        <v>1200</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>697</v>
+        <v>49827</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Yde et Olive</t>
+          <t>Reinbert</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8666,29 +8666,29 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1276</v>
+        <v>1201</v>
       </c>
       <c r="E266" t="n">
-        <v>1320</v>
+        <v>1267</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>48665</v>
+        <v>685</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Yde et Olive, court résumé</t>
+          <t>Renaut de Montauban</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8697,10 +8697,10 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1276</v>
+        <v>1401</v>
       </c>
       <c r="E267" t="n">
-        <v>1500</v>
+        <v>1445</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -8715,23 +8715,23 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>698</v>
+        <v>49807</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Yon de Metz ou la Venjance Fromondin</t>
+          <t>Renaut de Montauban, 1re version, Vulgate</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1254</v>
+        <v>1401</v>
       </c>
       <c r="E268" t="n">
-        <v>1260</v>
+        <v>1450</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -8746,23 +8746,23 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>699</v>
+        <v>49820</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Yonnet abrégé</t>
+          <t>Renaut de Montauban, 2e version (bourguignonne)</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1301</v>
+        <v>1462</v>
       </c>
       <c r="E269" t="n">
-        <v>1333</v>
+        <v>1462</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -8777,11 +8777,11 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>48670</v>
+        <v>49815</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Ysaïe le triste</t>
+          <t>Renaut de Montauban, abrégé</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8790,14 +8790,14 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1381</v>
+        <v>1401</v>
       </c>
       <c r="E270" t="n">
-        <v>1448</v>
+        <v>1500</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -8808,11 +8808,11 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>48766</v>
+        <v>758</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Yvain</t>
+          <t>Renier de Gennes</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8821,29 +8821,29 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1281</v>
+        <v>1351</v>
       </c>
       <c r="E271" t="n">
         <v>1400</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>609</v>
+        <v>703</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Bueve de Hanstonne cont. 4</t>
+          <t>Retour de Cornumaran</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1201</v>
+        <v>1151</v>
       </c>
       <c r="E272" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -8864,29 +8864,29 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>48677</v>
+        <v>773</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Ciperis de Vignevaux</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1451</v>
+        <v>1280</v>
       </c>
       <c r="E273" t="n">
-        <v>1468</v>
+        <v>1320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -8895,17 +8895,17 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>48942</v>
+        <v>50323</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Eledus et Serene</t>
+          <t>Couronnement de Louis, rédaction D (courte / archaïque)</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8914,29 +8914,29 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1251</v>
+        <v>1101</v>
       </c>
       <c r="E274" t="n">
-        <v>1288</v>
+        <v>1250</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>637</v>
+        <v>48546</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Enfances Renier</t>
+          <t>Richars li biaus</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8952,22 +8952,22 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>48958</v>
+        <v>690</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Hunbaut</t>
+          <t>Roland</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8976,14 +8976,14 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1226</v>
+        <v>1086</v>
       </c>
       <c r="E276" t="n">
-        <v>1300</v>
+        <v>1105</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -8994,11 +8994,11 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>50194</v>
+        <v>49777</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Joufroi de Poitiers</t>
+          <t>Roman de la Rose ou Guillaume de Dole</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1241</v>
+        <v>1201</v>
       </c>
       <c r="E277" t="n">
-        <v>1260</v>
+        <v>1232</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -9025,11 +9025,11 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>750</v>
+        <v>49753</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Prise de Cordres et de Sebille</t>
+          <t>Roman de la Violette ou Gérard de Nevers</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9038,45 +9038,45 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1191</v>
+        <v>1223</v>
       </c>
       <c r="E278" t="n">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>48787</v>
+        <v>49420</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Roland</t>
+          <t>Sept Sages de Rome, Version A/L</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>frm (Middle French)</t>
+          <t>fro (Old French)</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1401</v>
+        <v>1201</v>
       </c>
       <c r="E279" t="n">
-        <v>1433</v>
+        <v>1300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -9087,11 +9087,11 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>49290</v>
+        <v>49289</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Sept Sages de Rome, version C</t>
+          <t>Sept Sages de Rome, version K</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9100,10 +9100,10 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1167</v>
+        <v>1155</v>
       </c>
       <c r="E280" t="n">
-        <v>1250</v>
+        <v>1200</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -9118,11 +9118,11 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>48773</v>
+        <v>49483</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Sone de Nansay</t>
+          <t>Sept Sages de Rome, Version M</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9131,45 +9131,45 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1251</v>
+        <v>1281</v>
       </c>
       <c r="E281" t="n">
-        <v>1300</v>
+        <v>1320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>48381</v>
+        <v>49291</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Tristan et Iseut</t>
+          <t>Sept Sages, version D</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1146</v>
+        <v>1401</v>
       </c>
       <c r="E282" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -9180,11 +9180,11 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>48979</v>
+        <v>48982</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Yder</t>
+          <t>Silence</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1201</v>
+        <v>1251</v>
       </c>
       <c r="E283" t="n">
-        <v>1233</v>
+        <v>1300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -9211,23 +9211,23 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Agolant</t>
+          <t>Theseus de Cologne</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1180</v>
+        <v>1361</v>
       </c>
       <c r="E284" t="n">
-        <v>1220</v>
+        <v>1378</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -9236,29 +9236,29 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>715</v>
+        <v>48541</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Aquin</t>
+          <t>Theseus de Cologne, version abrégée</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1101</v>
+        <v>1401</v>
       </c>
       <c r="E285" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -9267,17 +9267,17 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>48817</v>
+        <v>694</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Berinus</t>
+          <t>Tristan de Nanteuil</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9286,29 +9286,29 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1241</v>
+        <v>1301</v>
       </c>
       <c r="E286" t="n">
-        <v>1260</v>
+        <v>1380</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>50227</v>
+        <v>48520</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Chanson de geste non identifiée (Lorrains?; fragment d'Oxford)</t>
+          <t>Troie, prose 2</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9317,14 +9317,14 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1101</v>
+        <v>1281</v>
       </c>
       <c r="E287" t="n">
-        <v>1260</v>
+        <v>1297</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -9335,11 +9335,11 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>710</v>
+        <v>48522</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Destruction de Rome</t>
+          <t>Troie, prose 4</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9348,14 +9348,14 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1170</v>
+        <v>1281</v>
       </c>
       <c r="E288" t="n">
-        <v>1170</v>
+        <v>1300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -9366,27 +9366,27 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>711</v>
+        <v>48519</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Gormont et Isembart</t>
+          <t>Troise, prose 1 remaniée</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1068</v>
+        <v>1401</v>
       </c>
       <c r="E289" t="n">
-        <v>1130</v>
+        <v>1500</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -9397,11 +9397,11 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>766</v>
+        <v>695</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Lohier et Malart</t>
+          <t>Venjance Nostre Seigneur</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9410,29 +9410,29 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1301</v>
+        <v>1181</v>
       </c>
       <c r="E290" t="n">
-        <v>1350</v>
+        <v>1220</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>742</v>
+        <v>48770</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Mainet</t>
+          <t>Wistasse le moine</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9441,29 +9441,29 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1151</v>
+        <v>1201</v>
       </c>
       <c r="E291" t="n">
-        <v>1200</v>
+        <v>1284</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>48703</v>
+        <v>697</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Mainet</t>
+          <t>Yde et Olive</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9472,10 +9472,10 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1201</v>
+        <v>1276</v>
       </c>
       <c r="E292" t="n">
-        <v>1220</v>
+        <v>1320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -9490,27 +9490,27 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>48989</v>
+        <v>48665</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Merlin</t>
+          <t>Yde et Olive, court résumé</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1191</v>
+        <v>1276</v>
       </c>
       <c r="E293" t="n">
-        <v>1205</v>
+        <v>1500</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -9521,11 +9521,11 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>767</v>
+        <v>698</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Moniage Guillaume fragm.</t>
+          <t>Yon de Metz ou la Venjance Fromondin</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9534,10 +9534,10 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1181</v>
+        <v>1254</v>
       </c>
       <c r="E294" t="n">
-        <v>1220</v>
+        <v>1260</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -9552,11 +9552,11 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>49850</v>
+        <v>699</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Narbonnais / Siege de Narbonne</t>
+          <t>Yonnet abrégé</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9565,10 +9565,10 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1196</v>
+        <v>1301</v>
       </c>
       <c r="E295" t="n">
-        <v>1205</v>
+        <v>1333</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -9583,27 +9583,27 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>753</v>
+        <v>48670</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Reine Sébile</t>
+          <t>Ysaïe le triste</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1246</v>
+        <v>1381</v>
       </c>
       <c r="E296" t="n">
-        <v>1255</v>
+        <v>1448</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -9614,27 +9614,27 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>48386</v>
+        <v>48766</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Siege d'Orange</t>
+          <t>Yvain</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1161</v>
+        <v>1281</v>
       </c>
       <c r="E297" t="n">
-        <v>1180</v>
+        <v>1400</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -9645,11 +9645,11 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>771</v>
+        <v>609</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Syracon</t>
+          <t>Bueve de Hanstonne cont. 4</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9658,60 +9658,60 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1180</v>
+        <v>1201</v>
       </c>
       <c r="E298" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>48523</v>
+        <v>48677</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Troie, prose 5</t>
+          <t>Ciperis de Vignevaux</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>fro (Old French)</t>
+          <t>frm (Middle French)</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1301</v>
+        <v>1451</v>
       </c>
       <c r="E299" t="n">
-        <v>1320</v>
+        <v>1468</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>696</v>
+        <v>48942</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Vivien de Monbranc</t>
+          <t>Eledus et Serene</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9720,29 +9720,29 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1200</v>
+        <v>1251</v>
       </c>
       <c r="E300" t="n">
-        <v>1320</v>
+        <v>1288</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>48705</v>
+        <v>637</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Huon de Bordeaux</t>
+          <t>Enfances Renier</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1201</v>
+        <v>1251</v>
       </c>
       <c r="E301" t="n">
         <v>1300</v>
